--- a/scanner_trade_log.xlsx
+++ b/scanner_trade_log.xlsx
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="48" min="1" max="1"/>
@@ -4680,4423 +4680,7803 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="48" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="48" t="n">
         <v>68.48</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="48" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="48" t="n">
         <v>68.03</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" s="48" t="n">
         <v>4.5</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="48" t="n">
         <v>80</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K76" t="n">
+      <c r="K76" s="48" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76" s="48" t="n">
         <v>1.12</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76" s="48" t="n">
         <v>0.01636</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N76" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="48" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="48" t="n">
         <v>181.2</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="48" t="n">
         <v>182.8</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="48" t="n">
         <v>180.56</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="48" t="n">
         <v>78</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K77" t="n">
+      <c r="K77" s="48" t="n">
         <v>182.8</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77" s="48" t="n">
         <v>0.008829999999999999</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="48" t="inlineStr">
         <is>
           <t>MDLZ</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="48" t="n">
         <v>57.07</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="48" t="n">
         <v>57.42</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="48" t="n">
         <v>56.93</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="48" t="n">
         <v>78</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K78" t="n">
+      <c r="K78" s="48" t="n">
         <v>56.93</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78" s="48" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M78" s="48" t="n">
         <v>-0.00245</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N78" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="48" t="inlineStr">
         <is>
           <t>TMUS</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="48" t="n">
         <v>197.06</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="48" t="n">
         <v>198.46</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="48" t="n">
         <v>196.5</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="48" t="n">
         <v>76</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="K79" s="48" t="n">
         <v>196.5</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79" s="48" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M79" s="48" t="n">
         <v>-0.00284</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="48" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="48" t="n">
         <v>278.27</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="48" t="n">
         <v>282.82</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="48" t="n">
         <v>276.45</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" s="48" t="n">
         <v>4.7</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K80" t="n">
+      <c r="K80" s="48" t="n">
         <v>276.45</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80" s="48" t="n">
         <v>-1.82</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M80" s="48" t="n">
         <v>-0.00654</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="48" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="48" t="n">
         <v>420.05</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="48" t="n">
         <v>423.68</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="48" t="n">
         <v>418.6</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" s="48" t="n">
         <v>2.9</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="K81" s="48" t="n">
         <v>423.68</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81" s="48" t="n">
         <v>3.63</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M81" s="48" t="n">
         <v>0.00864</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="48" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="48" t="n">
         <v>134.46</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="48" t="n">
         <v>135.46</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="48" t="n">
         <v>134.06</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" s="48" t="n">
         <v>5.1</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="48" t="n">
         <v>52</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K82" t="n">
+      <c r="K82" s="48" t="n">
         <v>135.46</v>
       </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="n">
+      <c r="L82" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="48" t="n">
         <v>0.00744</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="48" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="48" t="n">
         <v>158.36</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="48" t="n">
         <v>160.29</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="48" t="n">
         <v>157.59</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" s="48" t="n">
         <v>10.5</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="K83" s="48" t="n">
         <v>157.59</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83" s="48" t="n">
         <v>-0.77</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M83" s="48" t="n">
         <v>-0.00486</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="48" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="48" t="n">
         <v>584.11</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="48" t="n">
         <v>588.88</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="48" t="n">
         <v>582.2</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" s="48" t="n">
         <v>3.4</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K84" t="n">
+      <c r="K84" s="48" t="n">
         <v>582.2</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84" s="48" t="n">
         <v>-1.91</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84" s="48" t="n">
         <v>-0.00327</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="48" t="inlineStr">
         <is>
           <t>09:31</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="48" t="inlineStr">
         <is>
           <t>MARA</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="48" t="n">
         <v>11.53</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="48" t="n">
         <v>11.93</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="48" t="n">
         <v>11.37</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" s="48" t="n">
         <v>5.7</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="K85" s="48" t="n">
         <v>11.93</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85" s="48" t="n">
         <v>0.4</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M85" s="48" t="n">
         <v>0.03469</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="48" t="inlineStr">
         <is>
           <t>09:59</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="48" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="48" t="n">
         <v>276.87</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="48" t="n">
         <v>280.47</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="48" t="n">
         <v>275.43</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="48" t="n">
         <v>278.57</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="48" t="n">
         <v>0.00614</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="48" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="48" t="n">
         <v>158.68</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="48" t="n">
         <v>161.71</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="48" t="n">
         <v>157.47</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" s="48" t="n">
         <v>2.1</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K87" t="n">
+      <c r="K87" s="48" t="n">
         <v>157.47</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87" s="48" t="n">
         <v>-1.21</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87" s="48" t="n">
         <v>-0.00763</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="48" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="48" t="n">
         <v>277.57</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="48" t="n">
         <v>281.42</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="48" t="n">
         <v>276.03</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" s="48" t="n">
         <v>5.5</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="K88" s="48" t="n">
         <v>278.57</v>
       </c>
-      <c r="L88" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" t="n">
+      <c r="L88" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="48" t="n">
         <v>0.0036</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="48" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="48" t="n">
         <v>90.20999999999999</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="48" t="n">
         <v>93.73999999999999</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="48" t="n">
         <v>88.8</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89" s="48" t="n">
         <v>3.2</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="K89" s="48" t="n">
         <v>90.8</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89" s="48" t="n">
         <v>0.59</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M89" s="48" t="n">
         <v>0.00654</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="48" t="inlineStr">
         <is>
           <t>CRWD</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="48" t="n">
         <v>427.83</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="48" t="n">
         <v>438.48</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="48" t="n">
         <v>423.57</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90" s="48" t="n">
         <v>2.4</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K90" t="n">
+      <c r="K90" s="48" t="n">
         <v>423.57</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" s="48" t="n">
         <v>-4.26</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90" s="48" t="n">
         <v>-0.00996</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="48" t="inlineStr">
         <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="48" t="n">
         <v>124.5</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="48" t="n">
         <v>126.12</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="48" t="n">
         <v>123.85</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="K91" s="48" t="n">
         <v>126.12</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91" s="48" t="n">
         <v>1.62</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91" s="48" t="n">
         <v>0.01301</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="48" t="inlineStr">
         <is>
           <t>LLY</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="48" t="n">
         <v>923.1799999999999</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="48" t="n">
         <v>940.03</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="48" t="n">
         <v>916.4400000000001</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92" s="48" t="n">
         <v>1.9</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="K92" s="48" t="n">
         <v>926.73</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92" s="48" t="n">
         <v>3.55</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" s="48" t="n">
         <v>0.00385</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="48" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="48" t="n">
         <v>316.7</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="48" t="n">
         <v>319.92</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="48" t="n">
         <v>315.41</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" s="48" t="n">
         <v>2.9</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K93" t="n">
+      <c r="K93" s="48" t="n">
         <v>317.02</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93" s="48" t="n">
         <v>0.32</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93" s="48" t="n">
         <v>0.00101</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="48" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="48" t="n">
         <v>186.51</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="48" t="n">
         <v>190.74</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="48" t="n">
         <v>184.82</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94" s="48" t="n">
         <v>76</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K94" t="n">
+      <c r="K94" s="48" t="n">
         <v>184.82</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94" s="48" t="n">
         <v>-1.69</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94" s="48" t="n">
         <v>-0.00906</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="48" t="inlineStr">
         <is>
           <t>NKE</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="48" t="n">
         <v>46.13</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="48" t="n">
         <v>46.96</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="48" t="n">
         <v>45.8</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" s="48" t="n">
         <v>1.8</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" s="48" t="n">
         <v>58</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K95" t="n">
+      <c r="K95" s="48" t="n">
         <v>45.8</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="48" t="n">
         <v>-0.33</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" s="48" t="n">
         <v>-0.00715</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="48" t="inlineStr">
         <is>
           <t>10:01</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="48" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="48" t="n">
         <v>253.33</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="48" t="n">
         <v>257.06</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="48" t="n">
         <v>251.84</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K96" t="n">
+      <c r="K96" s="48" t="n">
         <v>251.84</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96" s="48" t="n">
         <v>-1.49</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M96" s="48" t="n">
         <v>-0.00588</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="48" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="48" t="n">
         <v>311.75</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="48" t="n">
         <v>318.77</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="48" t="n">
         <v>308.94</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="48" t="n">
         <v>84</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="K97" s="48" t="n">
         <v>308.94</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97" s="48" t="n">
         <v>-2.81</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" s="48" t="n">
         <v>-0.009010000000000001</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="48" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="48" t="n">
         <v>588.75</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="48" t="n">
         <v>596.98</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="48" t="n">
         <v>585.46</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98" s="48" t="n">
         <v>83</v>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="K98" s="48" t="n">
         <v>590.5</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98" s="48" t="n">
         <v>1.75</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M98" s="48" t="n">
         <v>0.00297</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="48" t="n">
         <v>121.71</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="48" t="n">
         <v>123.86</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="48" t="n">
         <v>120.85</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K99" t="n">
+      <c r="K99" s="48" t="n">
         <v>122.39</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99" s="48" t="n">
         <v>0.68</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M99" s="48" t="n">
         <v>0.00559</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="48" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="48" t="n">
         <v>266.58</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="48" t="n">
         <v>272.56</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="48" t="n">
         <v>264.19</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="48" t="n">
         <v>267.64</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100" s="48" t="n">
         <v>1.06</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M100" s="48" t="n">
         <v>0.00398</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="48" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="48" t="n">
         <v>229.98</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="48" t="n">
         <v>234.6</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="48" t="n">
         <v>228.13</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101" s="48" t="n">
         <v>2.6</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" s="48" t="n">
         <v>83</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K101" t="n">
+      <c r="K101" s="48" t="n">
         <v>228.13</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101" s="48" t="n">
         <v>-1.85</v>
       </c>
-      <c r="M101" t="n">
+      <c r="M101" s="48" t="n">
         <v>-0.00804</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="48" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="48" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="48" t="n">
         <v>95.02</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="48" t="n">
         <v>90.43000000000001</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102" s="48" t="n">
         <v>2.9</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K102" t="n">
+      <c r="K102" s="48" t="n">
         <v>90.43000000000001</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102" s="48" t="n">
         <v>-1.31</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M102" s="48" t="n">
         <v>-0.01428</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="48" t="inlineStr">
         <is>
           <t>BKNG</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="48" t="n">
         <v>190.66</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="48" t="n">
         <v>195.26</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="48" t="n">
         <v>188.82</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103" s="48" t="n">
         <v>1.3</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K103" t="n">
+      <c r="K103" s="48" t="n">
         <v>192.07</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103" s="48" t="n">
         <v>1.41</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M103" s="48" t="n">
         <v>0.0074</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N103" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="48" t="inlineStr">
         <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="48" t="n">
         <v>313.03</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="48" t="n">
         <v>316.38</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="48" t="n">
         <v>311.69</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K104" t="n">
+      <c r="K104" s="48" t="n">
         <v>311.69</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104" s="48" t="n">
         <v>-1.34</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M104" s="48" t="n">
         <v>-0.00428</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="48" t="inlineStr">
         <is>
           <t>UNH</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="48" t="n">
         <v>323.02</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="48" t="n">
         <v>327.44</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="48" t="n">
         <v>321.25</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K105" t="n">
+      <c r="K105" s="48" t="n">
         <v>324.51</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105" s="48" t="n">
         <v>1.49</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M105" s="48" t="n">
         <v>0.00461</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N105" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="48" t="inlineStr">
         <is>
           <t>10:31</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="48" t="inlineStr">
         <is>
           <t>RIVN</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="48" t="n">
         <v>17.39</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="48" t="n">
         <v>17.79</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="48" t="n">
         <v>17.23</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106" s="48" t="n">
         <v>2.1</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K106" t="n">
+      <c r="K106" s="48" t="n">
         <v>17.23</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106" s="48" t="n">
         <v>-0.16</v>
       </c>
-      <c r="M106" t="n">
+      <c r="M106" s="48" t="n">
         <v>-0.0092</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N106" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="48" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="48" t="n">
         <v>313.04</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="48" t="n">
         <v>318.84</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="48" t="n">
         <v>310.72</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H107" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I107" s="48" t="n">
         <v>77</v>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K107" t="n">
+      <c r="K107" s="48" t="n">
         <v>310.72</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L107" s="48" t="n">
         <v>-2.32</v>
       </c>
-      <c r="M107" t="n">
+      <c r="M107" s="48" t="n">
         <v>-0.00741</v>
       </c>
-      <c r="N107" t="n">
+      <c r="N107" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="48" t="inlineStr">
         <is>
           <t>BKNG</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="48" t="n">
         <v>192.51</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="48" t="n">
         <v>196.56</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="48" t="n">
         <v>190.89</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H108" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I108" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K108" t="n">
+      <c r="K108" s="48" t="n">
         <v>190.89</v>
       </c>
-      <c r="L108" t="n">
+      <c r="L108" s="48" t="n">
         <v>-1.62</v>
       </c>
-      <c r="M108" t="n">
+      <c r="M108" s="48" t="n">
         <v>-0.00842</v>
       </c>
-      <c r="N108" t="n">
+      <c r="N108" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="48" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="48" t="n">
         <v>254.15</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="48" t="n">
         <v>258.55</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" s="48" t="n">
         <v>252.39</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109" s="48" t="n">
         <v>3.3</v>
       </c>
-      <c r="H109" t="n">
+      <c r="H109" s="48" t="n">
         <v>75</v>
       </c>
-      <c r="I109" t="n">
+      <c r="I109" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K109" t="n">
+      <c r="K109" s="48" t="n">
         <v>252.39</v>
       </c>
-      <c r="L109" t="n">
+      <c r="L109" s="48" t="n">
         <v>-1.76</v>
       </c>
-      <c r="M109" t="n">
+      <c r="M109" s="48" t="n">
         <v>-0.00693</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N109" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="48" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="48" t="n">
         <v>85.58</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="48" t="n">
         <v>86.86</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="48" t="n">
         <v>85.06999999999999</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110" s="48" t="n">
         <v>3.1</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H110" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I110" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K110" t="n">
+      <c r="K110" s="48" t="n">
         <v>85.81</v>
       </c>
-      <c r="L110" t="n">
+      <c r="L110" s="48" t="n">
         <v>0.23</v>
       </c>
-      <c r="M110" t="n">
+      <c r="M110" s="48" t="n">
         <v>0.00263</v>
       </c>
-      <c r="N110" t="n">
+      <c r="N110" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="48" t="inlineStr">
         <is>
           <t>SNAP</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="48" t="n">
         <v>6.07</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="48" t="n">
         <v>6.24</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H111" s="48" t="n">
         <v>52</v>
       </c>
-      <c r="I111" t="n">
+      <c r="I111" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K111" t="n">
+      <c r="K111" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="L111" t="n">
+      <c r="L111" s="48" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="M111" t="n">
+      <c r="M111" s="48" t="n">
         <v>-0.01153</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N111" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="48" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="48" t="n">
         <v>92.65000000000001</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="48" t="n">
         <v>95.72</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="48" t="n">
         <v>91.42</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112" s="48" t="n">
         <v>2.4</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H112" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I112" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K112" t="n">
+      <c r="K112" s="48" t="n">
         <v>91.42</v>
       </c>
-      <c r="L112" t="n">
+      <c r="L112" s="48" t="n">
         <v>-1.23</v>
       </c>
-      <c r="M112" t="n">
+      <c r="M112" s="48" t="n">
         <v>-0.01328</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N112" s="48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="48" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="48" t="n">
         <v>147.09</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="48" t="n">
         <v>148.84</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" s="48" t="n">
         <v>146.39</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H113" t="n">
+      <c r="H113" s="48" t="n">
         <v>75</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I113" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K113" t="n">
+      <c r="K113" s="48" t="n">
         <v>146.92</v>
       </c>
-      <c r="L113" t="n">
+      <c r="L113" s="48" t="n">
         <v>-0.17</v>
       </c>
-      <c r="M113" t="n">
+      <c r="M113" s="48" t="n">
         <v>-0.00116</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N113" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="48" t="inlineStr">
         <is>
           <t>UNP</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="48" t="n">
         <v>254.94</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="48" t="n">
         <v>257.74</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="48" t="n">
         <v>253.82</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="48" t="n">
         <v>1.9</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="48" t="n">
         <v>75</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K114" t="n">
+      <c r="K114" s="48" t="n">
         <v>253.82</v>
       </c>
-      <c r="L114" t="n">
+      <c r="L114" s="48" t="n">
         <v>-1.12</v>
       </c>
-      <c r="M114" t="n">
+      <c r="M114" s="48" t="n">
         <v>-0.00439</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N114" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="48" t="inlineStr">
         <is>
           <t>HON</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="48" t="n">
         <v>235.67</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="48" t="n">
         <v>239.04</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="48" t="n">
         <v>234.32</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115" s="48" t="n">
         <v>1.8</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K115" t="n">
+      <c r="K115" s="48" t="n">
         <v>234.32</v>
       </c>
-      <c r="L115" t="n">
+      <c r="L115" s="48" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M115" s="48" t="n">
         <v>-0.00573</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N115" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="48" t="inlineStr">
         <is>
           <t>11:01</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="48" t="inlineStr">
         <is>
           <t>MMM</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="48" t="n">
         <v>155.88</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="48" t="n">
         <v>158.13</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="48" t="n">
         <v>154.98</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I116" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J116" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K116" t="n">
+      <c r="K116" s="48" t="n">
         <v>154.98</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L116" s="48" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M116" s="48" t="n">
         <v>-0.00577</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N116" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="48" t="inlineStr">
         <is>
           <t>ISRG</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="48" t="n">
         <v>470.4</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="48" t="n">
         <v>476.32</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="48" t="n">
         <v>468.03</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H117" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I117" t="n">
+      <c r="I117" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K117" t="n">
+      <c r="K117" s="48" t="n">
         <v>468.03</v>
       </c>
-      <c r="L117" t="n">
+      <c r="L117" s="48" t="n">
         <v>-2.37</v>
       </c>
-      <c r="M117" t="n">
+      <c r="M117" s="48" t="n">
         <v>-0.00504</v>
       </c>
-      <c r="N117" t="n">
+      <c r="N117" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="48" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="48" t="n">
         <v>92.19</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="48" t="n">
         <v>95.22</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="48" t="n">
         <v>90.98</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" s="48" t="n">
         <v>2.7</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H118" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="I118" t="n">
+      <c r="I118" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K118" t="n">
+      <c r="K118" s="48" t="n">
         <v>90.98</v>
       </c>
-      <c r="L118" t="n">
+      <c r="L118" s="48" t="n">
         <v>-1.21</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M118" s="48" t="n">
         <v>-0.01313</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N118" s="48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="48" t="n">
         <v>122.07</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="48" t="n">
         <v>123.87</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="48" t="n">
         <v>121.35</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="I119" t="n">
+      <c r="I119" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="J119" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K119" t="n">
+      <c r="K119" s="48" t="n">
         <v>122.39</v>
       </c>
-      <c r="L119" t="n">
+      <c r="L119" s="48" t="n">
         <v>0.32</v>
       </c>
-      <c r="M119" t="n">
+      <c r="M119" s="48" t="n">
         <v>0.00262</v>
       </c>
-      <c r="N119" t="n">
+      <c r="N119" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="48" t="inlineStr">
         <is>
           <t>RIVN</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="48" t="n">
         <v>17.45</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="48" t="n">
         <v>17.94</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="48" t="n">
         <v>17.24</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I120" t="n">
+      <c r="I120" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K120" t="n">
+      <c r="K120" s="48" t="n">
         <v>17.24</v>
       </c>
-      <c r="L120" t="n">
+      <c r="L120" s="48" t="n">
         <v>-0.21</v>
       </c>
-      <c r="M120" t="n">
+      <c r="M120" s="48" t="n">
         <v>-0.01203</v>
       </c>
-      <c r="N120" t="n">
+      <c r="N120" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="48" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="48" t="n">
         <v>386.68</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="48" t="n">
         <v>391.1</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="48" t="n">
         <v>384.91</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I121" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K121" t="n">
+      <c r="K121" s="48" t="n">
         <v>391.1</v>
       </c>
-      <c r="L121" t="n">
+      <c r="L121" s="48" t="n">
         <v>4.42</v>
       </c>
-      <c r="M121" t="n">
+      <c r="M121" s="48" t="n">
         <v>0.01143</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N121" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="48" t="inlineStr">
         <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="48" t="inlineStr">
         <is>
           <t>CAT</t>
         </is>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="48" t="n">
         <v>790.97</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="48" t="n">
         <v>802.4</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="48" t="n">
         <v>786.4</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H122" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="I122" t="n">
+      <c r="I122" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K122" t="n">
+      <c r="K122" s="48" t="n">
         <v>794.47</v>
       </c>
-      <c r="L122" t="n">
+      <c r="L122" s="48" t="n">
         <v>3.5</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" s="48" t="n">
         <v>0.00442</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N122" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="48" t="inlineStr">
         <is>
           <t>11:28</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="48" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="48" t="n">
         <v>75.84</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="48" t="n">
         <v>76.42</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="48" t="n">
         <v>75.61</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123" s="48" t="n">
         <v>6.2</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H123" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I123" t="n">
+      <c r="I123" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K123" t="n">
+      <c r="K123" s="48" t="n">
         <v>75.73999999999999</v>
       </c>
-      <c r="L123" t="n">
+      <c r="L123" s="48" t="n">
         <v>-0.1</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M123" s="48" t="n">
         <v>-0.00132</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N123" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="48" t="inlineStr">
         <is>
           <t>11:28</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="48" t="inlineStr">
         <is>
           <t>TMO</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="48" t="n">
         <v>528.05</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="48" t="n">
         <v>534.97</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="48" t="n">
         <v>525.28</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124" s="48" t="n">
         <v>1.8</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H124" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I124" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K124" t="n">
+      <c r="K124" s="48" t="n">
         <v>525.28</v>
       </c>
-      <c r="L124" t="n">
+      <c r="L124" s="48" t="n">
         <v>-2.77</v>
       </c>
-      <c r="M124" t="n">
+      <c r="M124" s="48" t="n">
         <v>-0.00525</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N124" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="48" t="inlineStr">
         <is>
           <t>11:31</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="48" t="n">
         <v>122.15</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="48" t="n">
         <v>123.9</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="48" t="n">
         <v>121.45</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125" s="48" t="n">
         <v>3.3</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H125" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="I125" t="n">
+      <c r="I125" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K125" t="n">
+      <c r="K125" s="48" t="n">
         <v>122.39</v>
       </c>
-      <c r="L125" t="n">
+      <c r="L125" s="48" t="n">
         <v>0.24</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M125" s="48" t="n">
         <v>0.00196</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N125" s="48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="48" t="inlineStr">
         <is>
           <t>11:31</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="48" t="inlineStr">
         <is>
           <t>ISRG</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="48" t="n">
         <v>470.25</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="48" t="n">
         <v>476.1</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="48" t="n">
         <v>467.91</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H126" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="I126" t="n">
+      <c r="I126" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K126" t="n">
+      <c r="K126" s="48" t="n">
         <v>467.91</v>
       </c>
-      <c r="L126" t="n">
+      <c r="L126" s="48" t="n">
         <v>-2.34</v>
       </c>
-      <c r="M126" t="n">
+      <c r="M126" s="48" t="n">
         <v>-0.00498</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N126" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="48" t="inlineStr">
         <is>
           <t>11:31</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="48" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="48" t="n">
         <v>92.38</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="48" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="48" t="n">
         <v>91.19</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" s="48" t="n">
         <v>4.3</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="I127" t="n">
+      <c r="I127" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K127" t="n">
+      <c r="K127" s="48" t="n">
         <v>91.19</v>
       </c>
-      <c r="L127" t="n">
+      <c r="L127" s="48" t="n">
         <v>-1.19</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M127" s="48" t="n">
         <v>-0.01288</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N127" s="48" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="48" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="48" t="n">
         <v>253.82</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="48" t="n">
         <v>257.12</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="48" t="n">
         <v>252.5</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="48" t="n">
         <v>81</v>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="48" t="n">
         <v>252.5</v>
       </c>
-      <c r="L128" t="n">
+      <c r="L128" s="48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="M128" t="n">
+      <c r="M128" s="48" t="n">
         <v>-0.0052</v>
       </c>
-      <c r="N128" t="n">
+      <c r="N128" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="48" t="n">
         <v>122.9</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="48" t="n">
         <v>124.62</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" s="48" t="n">
         <v>122.21</v>
       </c>
-      <c r="G129" t="n">
+      <c r="G129" s="48" t="n">
         <v>1.8</v>
       </c>
-      <c r="H129" t="n">
+      <c r="H129" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I129" t="n">
+      <c r="I129" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K129" t="n">
+      <c r="K129" s="48" t="n">
         <v>122.21</v>
       </c>
-      <c r="L129" t="n">
+      <c r="L129" s="48" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M129" s="48" t="n">
         <v>-0.00561</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N129" s="48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="48" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="48" t="n">
         <v>136.36</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="48" t="n">
         <v>137.54</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" s="48" t="n">
         <v>135.89</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H130" t="n">
+      <c r="H130" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="I130" t="n">
+      <c r="I130" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K130" t="n">
+      <c r="K130" s="48" t="n">
         <v>135.89</v>
       </c>
-      <c r="L130" t="n">
+      <c r="L130" s="48" t="n">
         <v>-0.47</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M130" s="48" t="n">
         <v>-0.00345</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N130" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="48" t="inlineStr">
         <is>
           <t>BKNG</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="48" t="n">
         <v>191.88</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="48" t="n">
         <v>194.98</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" s="48" t="n">
         <v>190.64</v>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H131" t="n">
+      <c r="H131" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="I131" t="n">
+      <c r="I131" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K131" t="n">
+      <c r="K131" s="48" t="n">
         <v>190.64</v>
       </c>
-      <c r="L131" t="n">
+      <c r="L131" s="48" t="n">
         <v>-1.24</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M131" s="48" t="n">
         <v>-0.00646</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N131" s="48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="48" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="48" t="n">
         <v>350.54</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="48" t="n">
         <v>354.49</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" s="48" t="n">
         <v>348.96</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" s="48" t="n">
         <v>2.3</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H132" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I132" t="n">
+      <c r="I132" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K132" t="n">
+      <c r="K132" s="48" t="n">
         <v>348.96</v>
       </c>
-      <c r="L132" t="n">
+      <c r="L132" s="48" t="n">
         <v>-1.58</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M132" s="48" t="n">
         <v>-0.00451</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N132" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="48" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="48" t="n">
         <v>355.54</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="48" t="n">
         <v>359.24</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" s="48" t="n">
         <v>354.06</v>
       </c>
-      <c r="G133" t="n">
+      <c r="G133" s="48" t="n">
         <v>2.3</v>
       </c>
-      <c r="H133" t="n">
+      <c r="H133" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="I133" t="n">
+      <c r="I133" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K133" t="n">
+      <c r="K133" s="48" t="n">
         <v>355.23</v>
       </c>
-      <c r="L133" t="n">
+      <c r="L133" s="48" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M133" t="n">
+      <c r="M133" s="48" t="n">
         <v>-0.00087</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N133" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="48" t="inlineStr">
         <is>
           <t>SHW</t>
         </is>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="48" t="n">
         <v>349.04</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="48" t="n">
         <v>353.74</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="48" t="n">
         <v>347.16</v>
       </c>
-      <c r="G134" t="n">
+      <c r="G134" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H134" t="n">
+      <c r="H134" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I134" t="n">
+      <c r="I134" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K134" t="n">
+      <c r="K134" s="48" t="n">
         <v>347.16</v>
       </c>
-      <c r="L134" t="n">
+      <c r="L134" s="48" t="n">
         <v>-1.88</v>
       </c>
-      <c r="M134" t="n">
+      <c r="M134" s="48" t="n">
         <v>-0.00539</v>
       </c>
-      <c r="N134" t="n">
+      <c r="N134" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="48" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="48" t="n">
         <v>212.97</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="48" t="n">
         <v>219.94</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" s="48" t="n">
         <v>210.18</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G135" s="48" t="n">
         <v>2.1</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H135" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I135" t="n">
+      <c r="I135" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="K135" s="48" t="n">
         <v>210.18</v>
       </c>
-      <c r="L135" t="n">
+      <c r="L135" s="48" t="n">
         <v>-2.79</v>
       </c>
-      <c r="M135" t="n">
+      <c r="M135" s="48" t="n">
         <v>-0.0131</v>
       </c>
-      <c r="N135" t="n">
+      <c r="N135" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="48" t="inlineStr">
         <is>
           <t>USB</t>
         </is>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="48" t="n">
         <v>57.27</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="48" t="n">
         <v>57.9</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" s="48" t="n">
         <v>57.02</v>
       </c>
-      <c r="G136" t="n">
+      <c r="G136" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H136" t="n">
+      <c r="H136" s="48" t="n">
         <v>79</v>
       </c>
-      <c r="I136" t="n">
+      <c r="I136" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="K136" s="48" t="n">
         <v>57.02</v>
       </c>
-      <c r="L136" t="n">
+      <c r="L136" s="48" t="n">
         <v>-0.25</v>
       </c>
-      <c r="M136" t="n">
+      <c r="M136" s="48" t="n">
         <v>-0.00437</v>
       </c>
-      <c r="N136" t="n">
+      <c r="N136" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="48" t="inlineStr">
         <is>
           <t>12:02</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="48" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="48" t="n">
         <v>82.29000000000001</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="48" t="n">
         <v>83.36</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" s="48" t="n">
         <v>81.86</v>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H137" t="n">
+      <c r="H137" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="I137" t="n">
+      <c r="I137" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K137" t="n">
+      <c r="K137" s="48" t="n">
         <v>81.86</v>
       </c>
-      <c r="L137" t="n">
+      <c r="L137" s="48" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M137" t="n">
+      <c r="M137" s="48" t="n">
         <v>-0.00523</v>
       </c>
-      <c r="N137" t="n">
+      <c r="N137" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="48" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="48" t="n">
         <v>253.06</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="48" t="n">
         <v>256.11</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" s="48" t="n">
         <v>251.84</v>
       </c>
-      <c r="G138" t="n">
+      <c r="G138" s="48" t="n">
         <v>1.8</v>
       </c>
-      <c r="H138" t="n">
+      <c r="H138" s="48" t="n">
         <v>58</v>
       </c>
-      <c r="I138" t="n">
+      <c r="I138" s="48" t="n">
         <v>75</v>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J138" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K138" t="n">
+      <c r="K138" s="48" t="n">
         <v>251.84</v>
       </c>
-      <c r="L138" t="n">
+      <c r="L138" s="48" t="n">
         <v>-1.22</v>
       </c>
-      <c r="M138" t="n">
+      <c r="M138" s="48" t="n">
         <v>-0.00482</v>
       </c>
-      <c r="N138" t="n">
+      <c r="N138" s="48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="48" t="inlineStr">
         <is>
           <t>TMO</t>
         </is>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="48" t="n">
         <v>528.72</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="48" t="n">
         <v>534.42</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" s="48" t="n">
         <v>526.4400000000001</v>
       </c>
-      <c r="G139" t="n">
+      <c r="G139" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H139" t="n">
+      <c r="H139" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="I139" t="n">
+      <c r="I139" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="K139" s="48" t="n">
         <v>526.4400000000001</v>
       </c>
-      <c r="L139" t="n">
+      <c r="L139" s="48" t="n">
         <v>-2.28</v>
       </c>
-      <c r="M139" t="n">
+      <c r="M139" s="48" t="n">
         <v>-0.00431</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N139" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="48" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="48" t="n">
         <v>125.6</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="48" t="n">
         <v>126.55</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="48" t="n">
         <v>125.22</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" s="48" t="n">
         <v>1.9</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H140" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="I140" t="n">
+      <c r="I140" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J140" s="48" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="K140" s="48" t="n">
         <v>126.55</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L140" s="48" t="n">
         <v>0.95</v>
       </c>
-      <c r="M140" t="n">
+      <c r="M140" s="48" t="n">
         <v>0.00756</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N140" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="48" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="48" t="n">
         <v>279.35</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="48" t="n">
         <v>282.75</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" s="48" t="n">
         <v>277.99</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" s="48" t="n">
         <v>2.5</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H141" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="I141" t="n">
+      <c r="I141" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J141" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K141" t="n">
+      <c r="K141" s="48" t="n">
         <v>277.99</v>
       </c>
-      <c r="L141" t="n">
+      <c r="L141" s="48" t="n">
         <v>-1.36</v>
       </c>
-      <c r="M141" t="n">
+      <c r="M141" s="48" t="n">
         <v>-0.00487</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N141" s="48" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="48" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="48" t="n">
         <v>226.91</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="48" t="n">
         <v>229.76</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="48" t="n">
         <v>225.77</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I142" t="n">
+      <c r="I142" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J142" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="K142" s="48" t="n">
         <v>225.77</v>
       </c>
-      <c r="L142" t="n">
+      <c r="L142" s="48" t="n">
         <v>-1.14</v>
       </c>
-      <c r="M142" t="n">
+      <c r="M142" s="48" t="n">
         <v>-0.00502</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N142" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="48" t="n">
         <v>122.52</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="48" t="n">
         <v>124.17</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" s="48" t="n">
         <v>121.86</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G143" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H143" t="n">
+      <c r="H143" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="I143" t="n">
+      <c r="I143" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J143" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K143" t="n">
+      <c r="K143" s="48" t="n">
         <v>121.86</v>
       </c>
-      <c r="L143" t="n">
+      <c r="L143" s="48" t="n">
         <v>-0.66</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M143" s="48" t="n">
         <v>-0.00539</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N143" s="48" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="48" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="48" t="inlineStr">
         <is>
           <t>EMR</t>
         </is>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="48" t="n">
         <v>146.16</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="48" t="n">
         <v>147.78</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" s="48" t="n">
         <v>145.51</v>
       </c>
-      <c r="G144" t="n">
+      <c r="G144" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H144" t="n">
+      <c r="H144" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="I144" t="n">
+      <c r="I144" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K144" t="n">
+      <c r="K144" s="48" t="n">
         <v>145.51</v>
       </c>
-      <c r="L144" t="n">
+      <c r="L144" s="48" t="n">
         <v>-0.65</v>
       </c>
-      <c r="M144" t="n">
+      <c r="M144" s="48" t="n">
         <v>-0.00445</v>
       </c>
-      <c r="N144" t="n">
+      <c r="N144" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="48" t="inlineStr">
         <is>
           <t>12:31</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="48" t="inlineStr">
         <is>
           <t>PNC</t>
         </is>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="48" t="n">
         <v>224.9</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="48" t="n">
         <v>226.72</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" s="48" t="n">
         <v>224.17</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G145" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H145" t="n">
+      <c r="H145" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="I145" t="n">
+      <c r="I145" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="J145" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K145" t="n">
+      <c r="K145" s="48" t="n">
         <v>224.17</v>
       </c>
-      <c r="L145" t="n">
+      <c r="L145" s="48" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M145" t="n">
+      <c r="M145" s="48" t="n">
         <v>-0.00325</v>
       </c>
-      <c r="N145" t="n">
+      <c r="N145" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="48" t="inlineStr">
         <is>
           <t>12:31</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="48" t="inlineStr">
         <is>
           <t>MMM</t>
         </is>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="48" t="n">
         <v>156.01</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="48" t="n">
         <v>157.41</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" s="48" t="n">
         <v>155.45</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G146" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H146" t="n">
+      <c r="H146" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="I146" t="n">
+      <c r="I146" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J146" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K146" t="n">
+      <c r="K146" s="48" t="n">
         <v>155.45</v>
       </c>
-      <c r="L146" t="n">
+      <c r="L146" s="48" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="M146" t="n">
+      <c r="M146" s="48" t="n">
         <v>-0.00359</v>
       </c>
-      <c r="N146" t="n">
+      <c r="N146" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="48" t="inlineStr">
         <is>
           <t>12:31</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="48" t="inlineStr">
         <is>
           <t>ZTS</t>
         </is>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="48" t="n">
         <v>122.67</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="48" t="n">
         <v>124.22</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" s="48" t="n">
         <v>122.05</v>
       </c>
-      <c r="G147" t="n">
+      <c r="G147" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H147" t="n">
+      <c r="H147" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="I147" t="n">
+      <c r="I147" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J147" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K147" t="n">
+      <c r="K147" s="48" t="n">
         <v>122.05</v>
       </c>
-      <c r="L147" t="n">
+      <c r="L147" s="48" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M147" t="n">
+      <c r="M147" s="48" t="n">
         <v>-0.00505</v>
       </c>
-      <c r="N147" t="n">
+      <c r="N147" s="48" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="48" t="inlineStr">
         <is>
           <t>12:31</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="48" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="48" t="n">
         <v>147.2</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="48" t="n">
         <v>148.32</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="48" t="n">
         <v>146.75</v>
       </c>
-      <c r="G148" t="n">
+      <c r="G148" s="48" t="n">
         <v>1.6</v>
       </c>
-      <c r="H148" t="n">
+      <c r="H148" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="I148" t="n">
+      <c r="I148" s="48" t="n">
         <v>60</v>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="J148" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K148" t="n">
+      <c r="K148" s="48" t="n">
         <v>146.75</v>
       </c>
-      <c r="L148" t="n">
+      <c r="L148" s="48" t="n">
         <v>-0.45</v>
       </c>
-      <c r="M148" t="n">
+      <c r="M148" s="48" t="n">
         <v>-0.00306</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N148" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="48" t="inlineStr">
         <is>
           <t>13:01</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="48" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="48" t="n">
         <v>252.97</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="48" t="n">
         <v>255.46</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="48" t="n">
         <v>251.96</v>
       </c>
-      <c r="G149" t="n">
+      <c r="G149" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H149" t="n">
+      <c r="H149" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I149" t="n">
+      <c r="I149" s="48" t="n">
         <v>80</v>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J149" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K149" t="n">
+      <c r="K149" s="48" t="n">
         <v>251.96</v>
       </c>
-      <c r="L149" t="n">
+      <c r="L149" s="48" t="n">
         <v>-1.01</v>
       </c>
-      <c r="M149" t="n">
+      <c r="M149" s="48" t="n">
         <v>-0.00399</v>
       </c>
-      <c r="N149" t="n">
+      <c r="N149" s="48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="48" t="inlineStr">
         <is>
           <t>13:01</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="48" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="48" t="n">
         <v>279.74</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="48" t="n">
         <v>282.39</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="48" t="n">
         <v>278.68</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G150" s="48" t="n">
         <v>2.1</v>
       </c>
-      <c r="H150" t="n">
+      <c r="H150" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="I150" t="n">
+      <c r="I150" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="J150" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K150" t="n">
+      <c r="K150" s="48" t="n">
         <v>278.68</v>
       </c>
-      <c r="L150" t="n">
+      <c r="L150" s="48" t="n">
         <v>-1.06</v>
       </c>
-      <c r="M150" t="n">
+      <c r="M150" s="48" t="n">
         <v>-0.00379</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N150" s="48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="48" t="inlineStr">
         <is>
           <t>13:01</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="48" t="inlineStr">
         <is>
           <t>SHW</t>
         </is>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="48" t="n">
         <v>349.24</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="48" t="n">
         <v>352.54</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="48" t="n">
         <v>347.92</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G151" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H151" t="n">
+      <c r="H151" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="I151" t="n">
+      <c r="I151" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="J151" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K151" t="n">
+      <c r="K151" s="48" t="n">
         <v>347.92</v>
       </c>
-      <c r="L151" t="n">
+      <c r="L151" s="48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="M151" t="n">
+      <c r="M151" s="48" t="n">
         <v>-0.00378</v>
       </c>
-      <c r="N151" t="n">
+      <c r="N151" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="48" t="inlineStr">
         <is>
           <t>13:31</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="48" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="48" t="n">
         <v>252.58</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="48" t="n">
         <v>255.1</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="48" t="n">
         <v>251.57</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G152" s="48" t="n">
         <v>2.2</v>
       </c>
-      <c r="H152" t="n">
+      <c r="H152" s="48" t="n">
         <v>51</v>
       </c>
-      <c r="I152" t="n">
+      <c r="I152" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="J152" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K152" t="n">
+      <c r="K152" s="48" t="n">
         <v>251.57</v>
       </c>
-      <c r="L152" t="n">
+      <c r="L152" s="48" t="n">
         <v>-1.01</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M152" s="48" t="n">
         <v>-0.004</v>
       </c>
-      <c r="N152" t="n">
+      <c r="N152" s="48" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="48" t="inlineStr">
         <is>
           <t>13:31</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="48" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="48" t="n">
         <v>197.72</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="48" t="n">
         <v>201.22</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="48" t="n">
         <v>196.32</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G153" s="48" t="n">
         <v>1.4</v>
       </c>
-      <c r="H153" t="n">
+      <c r="H153" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I153" t="n">
+      <c r="I153" s="48" t="n">
         <v>62</v>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="J153" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K153" t="n">
+      <c r="K153" s="48" t="n">
         <v>201.05</v>
       </c>
-      <c r="L153" t="n">
+      <c r="L153" s="48" t="n">
         <v>3.33</v>
       </c>
-      <c r="M153" t="n">
+      <c r="M153" s="48" t="n">
         <v>0.01684</v>
       </c>
-      <c r="N153" t="n">
+      <c r="N153" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="48" t="inlineStr">
         <is>
           <t>14:01</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C154" s="48" t="inlineStr">
         <is>
           <t>ARM</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="48" t="n">
         <v>167.22</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="48" t="n">
         <v>170.57</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="48" t="n">
         <v>165.88</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G154" s="48" t="n">
         <v>3.5</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H154" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I154" s="48" t="n">
         <v>78</v>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="J154" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K154" t="n">
+      <c r="K154" s="48" t="n">
         <v>165.88</v>
       </c>
-      <c r="L154" t="n">
+      <c r="L154" s="48" t="n">
         <v>-1.34</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M154" s="48" t="n">
         <v>-0.00801</v>
       </c>
-      <c r="N154" t="n">
+      <c r="N154" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="48" t="inlineStr">
         <is>
           <t>14:01</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="48" t="inlineStr">
         <is>
           <t>MCD</t>
         </is>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="48" t="n">
         <v>312.1</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="48" t="n">
         <v>313.8</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="48" t="n">
         <v>311.42</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G155" s="48" t="n">
         <v>2.1</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H155" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="I155" t="n">
+      <c r="I155" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="J155" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K155" t="n">
+      <c r="K155" s="48" t="n">
         <v>311.42</v>
       </c>
-      <c r="L155" t="n">
+      <c r="L155" s="48" t="n">
         <v>-0.68</v>
       </c>
-      <c r="M155" t="n">
+      <c r="M155" s="48" t="n">
         <v>-0.00218</v>
       </c>
-      <c r="N155" t="n">
+      <c r="N155" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="48" t="inlineStr">
         <is>
           <t>14:01</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C156" s="48" t="inlineStr">
         <is>
           <t>APD</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="48" t="n">
         <v>293.96</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="48" t="n">
         <v>296.14</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="48" t="n">
         <v>293.09</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G156" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H156" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I156" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="J156" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K156" t="n">
+      <c r="K156" s="48" t="n">
         <v>293.09</v>
       </c>
-      <c r="L156" t="n">
+      <c r="L156" s="48" t="n">
         <v>-0.87</v>
       </c>
-      <c r="M156" t="n">
+      <c r="M156" s="48" t="n">
         <v>-0.00296</v>
       </c>
-      <c r="N156" t="n">
+      <c r="N156" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="48" t="inlineStr">
         <is>
           <t>14:31</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="48" t="inlineStr">
         <is>
           <t>MDB</t>
         </is>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="48" t="n">
         <v>262.71</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="48" t="n">
         <v>272.28</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="48" t="n">
         <v>258.88</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G157" s="48" t="n">
         <v>5.2</v>
       </c>
-      <c r="H157" t="n">
+      <c r="H157" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="I157" t="n">
+      <c r="I157" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="J157" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K157" t="n">
+      <c r="K157" s="48" t="n">
         <v>263.2</v>
       </c>
-      <c r="L157" t="n">
+      <c r="L157" s="48" t="n">
         <v>0.49</v>
       </c>
-      <c r="M157" t="n">
+      <c r="M157" s="48" t="n">
         <v>0.00185</v>
       </c>
-      <c r="N157" t="n">
+      <c r="N157" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="48" t="inlineStr">
         <is>
           <t>15:01</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="48" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="48" t="n">
         <v>86.37</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="48" t="n">
         <v>86.94</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="48" t="n">
         <v>86.14</v>
       </c>
-      <c r="G158" t="n">
+      <c r="G158" s="48" t="n">
         <v>2.3</v>
       </c>
-      <c r="H158" t="n">
+      <c r="H158" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="I158" t="n">
+      <c r="I158" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="J158" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K158" t="n">
+      <c r="K158" s="48" t="n">
         <v>86.14</v>
       </c>
-      <c r="L158" t="n">
+      <c r="L158" s="48" t="n">
         <v>-0.23</v>
       </c>
-      <c r="M158" t="n">
+      <c r="M158" s="48" t="n">
         <v>-0.00266</v>
       </c>
-      <c r="N158" t="n">
+      <c r="N158" s="48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="48" t="inlineStr">
         <is>
           <t>15:01</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="48" t="inlineStr">
         <is>
           <t>FDX</t>
         </is>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="48" t="n">
         <v>392.35</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="48" t="n">
         <v>395.22</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="48" t="n">
         <v>391.2</v>
       </c>
-      <c r="G159" t="n">
+      <c r="G159" s="48" t="n">
         <v>1.7</v>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="I159" t="n">
+      <c r="I159" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="J159" s="48" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="K159" t="n">
+      <c r="K159" s="48" t="n">
         <v>391.2</v>
       </c>
-      <c r="L159" t="n">
+      <c r="L159" s="48" t="n">
         <v>-1.15</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M159" s="48" t="n">
         <v>-0.00293</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N159" s="48" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="48" t="inlineStr">
         <is>
           <t>15:01</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="48" t="inlineStr">
         <is>
           <t>MDB</t>
         </is>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="48" t="n">
         <v>261.71</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="48" t="n">
         <v>271.21</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="48" t="n">
         <v>257.91</v>
       </c>
-      <c r="G160" t="n">
+      <c r="G160" s="48" t="n">
         <v>2.6</v>
       </c>
-      <c r="H160" t="n">
+      <c r="H160" s="48" t="n">
         <v>59</v>
       </c>
-      <c r="I160" t="n">
+      <c r="I160" s="48" t="n">
         <v>61</v>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J160" s="48" t="inlineStr">
         <is>
           <t>EOD</t>
         </is>
       </c>
-      <c r="K160" t="n">
+      <c r="K160" s="48" t="n">
         <v>263.2</v>
       </c>
-      <c r="L160" t="n">
+      <c r="L160" s="48" t="n">
         <v>1.49</v>
       </c>
-      <c r="M160" t="n">
+      <c r="M160" s="48" t="n">
         <v>0.00567</v>
       </c>
-      <c r="N160" t="n">
+      <c r="N160" s="48" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="E161" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="F161" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>51</v>
+      </c>
+      <c r="I161" t="n">
+        <v>63</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.01164748807184954</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="E162" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="F162" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H162" t="n">
+        <v>65</v>
+      </c>
+      <c r="I162" t="n">
+        <v>60</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="L162" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-0.01946847960444991</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="E163" t="n">
+        <v>177.64</v>
+      </c>
+      <c r="F163" t="n">
+        <v>169.24</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>70</v>
+      </c>
+      <c r="I163" t="n">
+        <v>58</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.02009903874162533</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>159.66</v>
+      </c>
+      <c r="E164" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="F164" t="n">
+        <v>157.62</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>64</v>
+      </c>
+      <c r="I164" t="n">
+        <v>51</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>157.62</v>
+      </c>
+      <c r="L164" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-0.01277715144682445</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CRML</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="E165" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F165" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>48</v>
+      </c>
+      <c r="I165" t="n">
+        <v>46</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="L165" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M165" t="n">
+        <v>-0.03080766028309736</v>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>HIMS</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="E166" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="F166" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>64</v>
+      </c>
+      <c r="I166" t="n">
+        <v>76</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-0.02325581395348839</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>142.68</v>
+      </c>
+      <c r="E167" t="n">
+        <v>144.53</v>
+      </c>
+      <c r="F167" t="n">
+        <v>141.94</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H167" t="n">
+        <v>60</v>
+      </c>
+      <c r="I167" t="n">
+        <v>71</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>143.59</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.00637790860667225</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="E168" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H168" t="n">
+        <v>62</v>
+      </c>
+      <c r="I168" t="n">
+        <v>70</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.004128486557244956</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>203.37</v>
+      </c>
+      <c r="E169" t="n">
+        <v>207.52</v>
+      </c>
+      <c r="F169" t="n">
+        <v>201.71</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H169" t="n">
+        <v>64</v>
+      </c>
+      <c r="I169" t="n">
+        <v>69</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>204.81</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.007080690367310801</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>253.39</v>
+      </c>
+      <c r="E170" t="n">
+        <v>255.24</v>
+      </c>
+      <c r="F170" t="n">
+        <v>252.65</v>
+      </c>
+      <c r="G170" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H170" t="n">
+        <v>62</v>
+      </c>
+      <c r="I170" t="n">
+        <v>68</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>252.65</v>
+      </c>
+      <c r="L170" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-0.002920399384348162</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="E171" t="n">
+        <v>391.18</v>
+      </c>
+      <c r="F171" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="G171" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H171" t="n">
+        <v>74</v>
+      </c>
+      <c r="I171" t="n">
+        <v>66</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="L171" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-0.006838273530941226</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>263.05</v>
+      </c>
+      <c r="E172" t="n">
+        <v>270.18</v>
+      </c>
+      <c r="F172" t="n">
+        <v>260.2</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H172" t="n">
+        <v>55</v>
+      </c>
+      <c r="I172" t="n">
+        <v>64</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>264.11</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.004029652157384536</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>233.68</v>
+      </c>
+      <c r="E173" t="n">
+        <v>236.46</v>
+      </c>
+      <c r="F173" t="n">
+        <v>232.57</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H173" t="n">
+        <v>74</v>
+      </c>
+      <c r="I173" t="n">
+        <v>64</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>232.57</v>
+      </c>
+      <c r="L173" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-0.004750085587127755</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="E174" t="n">
+        <v>152.46</v>
+      </c>
+      <c r="F174" t="n">
+        <v>147.95</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H174" t="n">
+        <v>64</v>
+      </c>
+      <c r="I174" t="n">
+        <v>60</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>150.44</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0.008040739748056745</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="E175" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="F175" t="n">
+        <v>122.82</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H175" t="n">
+        <v>72</v>
+      </c>
+      <c r="I175" t="n">
+        <v>60</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>122.82</v>
+      </c>
+      <c r="L175" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-0.003650523241664662</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="E176" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="F176" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H176" t="n">
+        <v>66</v>
+      </c>
+      <c r="I176" t="n">
+        <v>55</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="L176" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-0.00429224308300391</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>158.26</v>
+      </c>
+      <c r="E177" t="n">
+        <v>160.01</v>
+      </c>
+      <c r="F177" t="n">
+        <v>157.56</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H177" t="n">
+        <v>52</v>
+      </c>
+      <c r="I177" t="n">
+        <v>54</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>157.56</v>
+      </c>
+      <c r="L177" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-0.00442310122583084</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="E178" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="F178" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H178" t="n">
+        <v>45</v>
+      </c>
+      <c r="I178" t="n">
+        <v>51</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0.0005913660555885016</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>751.7</v>
+      </c>
+      <c r="E179" t="n">
+        <v>760</v>
+      </c>
+      <c r="F179" t="n">
+        <v>748.38</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H179" t="n">
+        <v>52</v>
+      </c>
+      <c r="I179" t="n">
+        <v>49</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>748.38</v>
+      </c>
+      <c r="L179" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-0.004416655580683849</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>DUK</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>128.79</v>
+      </c>
+      <c r="E180" t="n">
+        <v>129.59</v>
+      </c>
+      <c r="F180" t="n">
+        <v>128.47</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H180" t="n">
+        <v>54</v>
+      </c>
+      <c r="I180" t="n">
+        <v>44</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>128.47</v>
+      </c>
+      <c r="L180" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-0.002484664958459455</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>128.51</v>
+      </c>
+      <c r="E181" t="n">
+        <v>131.61</v>
+      </c>
+      <c r="F181" t="n">
+        <v>127.27</v>
+      </c>
+      <c r="G181" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>69</v>
+      </c>
+      <c r="I181" t="n">
+        <v>77</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>127.27</v>
+      </c>
+      <c r="L181" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-0.009649054548284141</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="E182" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="F182" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H182" t="n">
+        <v>54</v>
+      </c>
+      <c r="I182" t="n">
+        <v>56</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="L182" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-0.002911051212937962</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BDX</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>158.31</v>
+      </c>
+      <c r="E183" t="n">
+        <v>159.42</v>
+      </c>
+      <c r="F183" t="n">
+        <v>157.88</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>47</v>
+      </c>
+      <c r="I183" t="n">
+        <v>49</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>157.88</v>
+      </c>
+      <c r="L183" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-0.002716189754279621</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>148.72</v>
+      </c>
+      <c r="E184" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="F184" t="n">
+        <v>148.08</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H184" t="n">
+        <v>56</v>
+      </c>
+      <c r="I184" t="n">
+        <v>48</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
+        <v>148.08</v>
+      </c>
+      <c r="L184" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-0.004303388918773443</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>245.93</v>
+      </c>
+      <c r="E185" t="n">
+        <v>251.73</v>
+      </c>
+      <c r="F185" t="n">
+        <v>243.61</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H185" t="n">
+        <v>53</v>
+      </c>
+      <c r="I185" t="n">
+        <v>46</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>251.73</v>
+      </c>
+      <c r="L185" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0.02358394665148613</v>
+      </c>
+      <c r="N185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="E186" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="F186" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>75</v>
+      </c>
+      <c r="I186" t="n">
+        <v>65</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="L186" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-0.00431671021242753</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>145.74</v>
+      </c>
+      <c r="E187" t="n">
+        <v>149.04</v>
+      </c>
+      <c r="F187" t="n">
+        <v>144.42</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H187" t="n">
+        <v>59</v>
+      </c>
+      <c r="I187" t="n">
+        <v>60</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>149.04</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0.0226430629888842</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>468.59</v>
+      </c>
+      <c r="E188" t="n">
+        <v>472.94</v>
+      </c>
+      <c r="F188" t="n">
+        <v>466.85</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H188" t="n">
+        <v>48</v>
+      </c>
+      <c r="I188" t="n">
+        <v>52</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>466.85</v>
+      </c>
+      <c r="L188" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="M188" t="n">
+        <v>-0.003713267461960248</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="E189" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="F189" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H189" t="n">
+        <v>54</v>
+      </c>
+      <c r="I189" t="n">
+        <v>49</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="L189" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-0.01392586524677452</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>251.42</v>
+      </c>
+      <c r="E190" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="F190" t="n">
+        <v>250.65</v>
+      </c>
+      <c r="G190" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H190" t="n">
+        <v>55</v>
+      </c>
+      <c r="I190" t="n">
+        <v>62</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0.007636623975817421</v>
+      </c>
+      <c r="N190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>129.24</v>
+      </c>
+      <c r="E191" t="n">
+        <v>130.44</v>
+      </c>
+      <c r="F191" t="n">
+        <v>128.76</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H191" t="n">
+        <v>54</v>
+      </c>
+      <c r="I191" t="n">
+        <v>57</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
+        <v>130.18</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.007273290003094999</v>
+      </c>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>315.32</v>
+      </c>
+      <c r="E192" t="n">
+        <v>317.12</v>
+      </c>
+      <c r="F192" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="G192" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H192" t="n">
+        <v>63</v>
+      </c>
+      <c r="I192" t="n">
+        <v>67</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>317.12</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0.005708486616770301</v>
+      </c>
+      <c r="N192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>936.03</v>
+      </c>
+      <c r="E193" t="n">
+        <v>942.96</v>
+      </c>
+      <c r="F193" t="n">
+        <v>933.26</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H193" t="n">
+        <v>69</v>
+      </c>
+      <c r="I193" t="n">
+        <v>64</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>933.26</v>
+      </c>
+      <c r="L193" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-0.00295930685982285</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>660.9</v>
+      </c>
+      <c r="E194" t="n">
+        <v>667.05</v>
+      </c>
+      <c r="F194" t="n">
+        <v>658.4400000000001</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H194" t="n">
+        <v>48</v>
+      </c>
+      <c r="I194" t="n">
+        <v>42</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>658.4400000000001</v>
+      </c>
+      <c r="L194" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-0.003722197004085221</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>189.48</v>
+      </c>
+      <c r="F195" t="n">
+        <v>186.57</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H195" t="n">
+        <v>74</v>
+      </c>
+      <c r="I195" t="n">
+        <v>71</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>186.57</v>
+      </c>
+      <c r="L195" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-0.004429028815368263</v>
+      </c>
+      <c r="N195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>226.74</v>
+      </c>
+      <c r="E196" t="n">
+        <v>228.06</v>
+      </c>
+      <c r="F196" t="n">
+        <v>226.21</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>52</v>
+      </c>
+      <c r="I196" t="n">
+        <v>67</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>227.03</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0.001278997971244562</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="E197" t="n">
+        <v>281.82</v>
+      </c>
+      <c r="F197" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="G197" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H197" t="n">
+        <v>54</v>
+      </c>
+      <c r="I197" t="n">
+        <v>60</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="L197" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-0.002894924946390287</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>194.74</v>
+      </c>
+      <c r="E198" t="n">
+        <v>196.17</v>
+      </c>
+      <c r="F198" t="n">
+        <v>194.17</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H198" t="n">
+        <v>62</v>
+      </c>
+      <c r="I198" t="n">
+        <v>45</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0.003902639416658061</v>
+      </c>
+      <c r="N198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>161.23</v>
+      </c>
+      <c r="E199" t="n">
+        <v>162.23</v>
+      </c>
+      <c r="F199" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H199" t="n">
+        <v>56</v>
+      </c>
+      <c r="I199" t="n">
+        <v>44</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="L199" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-0.002480927867022125</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>527.64</v>
+      </c>
+      <c r="E200" t="n">
+        <v>531.04</v>
+      </c>
+      <c r="F200" t="n">
+        <v>526.28</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H200" t="n">
+        <v>54</v>
+      </c>
+      <c r="I200" t="n">
+        <v>60</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>526.28</v>
+      </c>
+      <c r="L200" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-0.002577514972329645</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="E201" t="n">
+        <v>435.58</v>
+      </c>
+      <c r="F201" t="n">
+        <v>428.33</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H201" t="n">
+        <v>64</v>
+      </c>
+      <c r="I201" t="n">
+        <v>88</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>433.15</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.006389405204460967</v>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>225.25</v>
+      </c>
+      <c r="E202" t="n">
+        <v>226.22</v>
+      </c>
+      <c r="F202" t="n">
+        <v>224.86</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H202" t="n">
+        <v>57</v>
+      </c>
+      <c r="I202" t="n">
+        <v>60</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>224.86</v>
+      </c>
+      <c r="L202" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-0.001731409544949995</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AAOI</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>160.52</v>
+      </c>
+      <c r="E203" t="n">
+        <v>164.92</v>
+      </c>
+      <c r="F203" t="n">
+        <v>158.76</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H203" t="n">
+        <v>69</v>
+      </c>
+      <c r="I203" t="n">
+        <v>80</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K203" t="n">
+        <v>163.47</v>
+      </c>
+      <c r="L203" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.01837777224021922</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>144.29</v>
+      </c>
+      <c r="E204" t="n">
+        <v>145.01</v>
+      </c>
+      <c r="F204" t="n">
+        <v>144</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H204" t="n">
+        <v>59</v>
+      </c>
+      <c r="I204" t="n">
+        <v>68</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K204" t="n">
+        <v>145.01</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0.004989950793540778</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="E205" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="F205" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H205" t="n">
+        <v>64</v>
+      </c>
+      <c r="I205" t="n">
+        <v>68</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K205" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0.005306180983794702</v>
+      </c>
+      <c r="N205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>209.72</v>
+      </c>
+      <c r="E206" t="n">
+        <v>213.44</v>
+      </c>
+      <c r="F206" t="n">
+        <v>208.23</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H206" t="n">
+        <v>74</v>
+      </c>
+      <c r="I206" t="n">
+        <v>64</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K206" t="n">
+        <v>211.63</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0.0091073812702651</v>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E207" t="n">
+        <v>173.88</v>
+      </c>
+      <c r="F207" t="n">
+        <v>168.03</v>
+      </c>
+      <c r="G207" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H207" t="n">
+        <v>78</v>
+      </c>
+      <c r="I207" t="n">
+        <v>59</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>173.88</v>
+      </c>
+      <c r="L207" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0.02463170300530352</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="E208" t="n">
+        <v>173.02</v>
+      </c>
+      <c r="F208" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H208" t="n">
+        <v>80</v>
+      </c>
+      <c r="I208" t="n">
+        <v>53</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K208" t="n">
+        <v>170.81</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0.006422342682064597</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>151.96</v>
+      </c>
+      <c r="E209" t="n">
+        <v>153.49</v>
+      </c>
+      <c r="F209" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H209" t="n">
+        <v>50</v>
+      </c>
+      <c r="I209" t="n">
+        <v>43</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K209" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="L209" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-0.004014214266912435</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>170.31</v>
+      </c>
+      <c r="E210" t="n">
+        <v>172</v>
+      </c>
+      <c r="F210" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>72</v>
+      </c>
+      <c r="I210" t="n">
+        <v>76</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="L210" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-0.003875286242733818</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="E211" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="F211" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H211" t="n">
+        <v>64</v>
+      </c>
+      <c r="I211" t="n">
+        <v>74</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.00453277545327751</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>137.71</v>
+      </c>
+      <c r="E212" t="n">
+        <v>138.74</v>
+      </c>
+      <c r="F212" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>57</v>
+      </c>
+      <c r="I212" t="n">
+        <v>67</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>137.52</v>
+      </c>
+      <c r="L212" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-0.001379710986856421</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="E213" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="F213" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H213" t="n">
+        <v>76</v>
+      </c>
+      <c r="I213" t="n">
+        <v>58</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="L213" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M213" t="n">
+        <v>-0.001716738197424856</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AEVA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="E214" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="F214" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="G214" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H214" t="n">
+        <v>55</v>
+      </c>
+      <c r="I214" t="n">
+        <v>53</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.009590792838874589</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="E215" t="n">
+        <v>100.18</v>
+      </c>
+      <c r="F215" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H215" t="n">
+        <v>56</v>
+      </c>
+      <c r="I215" t="n">
+        <v>53</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-0.003017198028764069</v>
+      </c>
+      <c r="N215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>488.2</v>
+      </c>
+      <c r="E216" t="n">
+        <v>494.98</v>
+      </c>
+      <c r="F216" t="n">
+        <v>485.49</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H216" t="n">
+        <v>68</v>
+      </c>
+      <c r="I216" t="n">
+        <v>79</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>490.96</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.005653420729209322</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>313.01</v>
+      </c>
+      <c r="E217" t="n">
+        <v>314.61</v>
+      </c>
+      <c r="F217" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="G217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H217" t="n">
+        <v>44</v>
+      </c>
+      <c r="I217" t="n">
+        <v>41</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="L217" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-0.002044663109804755</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="E218" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F218" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H218" t="n">
+        <v>55</v>
+      </c>
+      <c r="I218" t="n">
+        <v>60</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.003900156006240166</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="E219" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="F219" t="n">
+        <v>274.87</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>68</v>
+      </c>
+      <c r="I219" t="n">
+        <v>58</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>274.87</v>
+      </c>
+      <c r="L219" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-0.00463516204961062</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="E220" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="F220" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H220" t="n">
+        <v>62</v>
+      </c>
+      <c r="I220" t="n">
+        <v>55</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L220" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-0.000512557662737138</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="E221" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F221" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H221" t="n">
+        <v>70</v>
+      </c>
+      <c r="I221" t="n">
+        <v>52</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>6</v>
+      </c>
+      <c r="L221" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-0.004975124378109493</v>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>401.79</v>
+      </c>
+      <c r="E222" t="n">
+        <v>405.64</v>
+      </c>
+      <c r="F222" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H222" t="n">
+        <v>63</v>
+      </c>
+      <c r="I222" t="n">
+        <v>69</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>404.83</v>
+      </c>
+      <c r="L222" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.00756614151671262</v>
+      </c>
+      <c r="N222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>264.07</v>
+      </c>
+      <c r="E223" t="n">
+        <v>266.35</v>
+      </c>
+      <c r="F223" t="n">
+        <v>263.17</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H223" t="n">
+        <v>55</v>
+      </c>
+      <c r="I223" t="n">
+        <v>59</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>263.17</v>
+      </c>
+      <c r="L223" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-0.003408187223084702</v>
+      </c>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>897.2</v>
+      </c>
+      <c r="E224" t="n">
+        <v>912.58</v>
+      </c>
+      <c r="F224" t="n">
+        <v>891.05</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H224" t="n">
+        <v>54</v>
+      </c>
+      <c r="I224" t="n">
+        <v>51</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>EOD</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>895.11</v>
+      </c>
+      <c r="L224" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-0.00232946946054395</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E225" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="F225" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H225" t="n">
+        <v>51</v>
+      </c>
+      <c r="I225" t="n">
+        <v>50</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="L225" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-0.002097168822090134</v>
+      </c>
+      <c r="N225" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9113,7 +12493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="48" min="1" max="2"/>
@@ -9296,6 +12676,45 @@
       <c r="G4" s="85">
         <f>SUM(G2:G3)</f>
         <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.0103</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10 post-close picks excluded; SQ resolved via XYZ ticker (Block rebrand)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9312,7 +12731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="48" min="1" max="1"/>
@@ -9932,6 +13351,411 @@
       <c r="G19" s="78">
         <f>IFERROR(D19/(D19+E19),"-")</f>
         <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
